--- a/Versuch_M6/Messdaten_M6_Kanja_Dagosto.xlsx
+++ b/Versuch_M6/Messdaten_M6_Kanja_Dagosto.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fynnlucca/Documents/Grundpraktikum-1/Versuch_M6/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4168B161-DBE2-6747-9A13-8C7343B24087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16CED41A-E99E-854F-91F1-58C5546F5962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" xr2:uid="{A220AA4E-B647-DB49-97EA-91DAD7FDB6F2}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20200" xr2:uid="{A220AA4E-B647-DB49-97EA-91DAD7FDB6F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="37">
   <si>
     <t>Versuch M6</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>RPM_AVG</t>
+  </si>
+  <si>
+    <t>Std. abweichung</t>
   </si>
 </sst>
 </file>
@@ -515,20 +518,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949B6FFE-B662-B942-AE71-95455D59FEBC}">
-  <dimension ref="A2:Q80"/>
+  <dimension ref="A2:R80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -536,12 +539,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" t="s">
         <v>2</v>
       </c>
@@ -552,7 +555,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -569,7 +572,7 @@
         <v>86.8</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>7</v>
       </c>
@@ -583,7 +586,7 @@
         <v>86.8</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" t="s">
         <v>10</v>
       </c>
@@ -623,8 +626,11 @@
       <c r="Q12" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -671,8 +677,12 @@
         <f>AVERAGE(C13:N13)</f>
         <v>655.48333333333323</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13">
+        <f>STDEV(C13:N13)</f>
+        <v>27.553380697816156</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>7</v>
       </c>
